--- a/exports/trend_1d/MARUTI_full_report.xlsx
+++ b/exports/trend_1d/MARUTI_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>6.82</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42040</v>
+        <v>42041</v>
       </c>
       <c r="H2" t="n">
-        <v>3522.7</v>
+        <v>3502.6</v>
       </c>
       <c r="I2" t="n">
         <v>3515.46583644273</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.84</v>
+        <v>-3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="M2" t="n">
         <v>0.29</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>6.92</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42062</v>
+        <v>42065</v>
       </c>
       <c r="H3" t="n">
-        <v>3604.4</v>
+        <v>3711.45</v>
       </c>
       <c r="I3" t="n">
         <v>3670.922910875313</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.91</v>
+        <v>-5.96</v>
       </c>
       <c r="L3" t="n">
-        <v>4.21</v>
+        <v>6.49</v>
       </c>
       <c r="M3" t="n">
-        <v>0.79</v>
+        <v>1.21</v>
       </c>
       <c r="N3" t="n">
         <v>3.08</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>7.51</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42114</v>
+        <v>42115</v>
       </c>
       <c r="H4" t="n">
-        <v>3608.05</v>
+        <v>3490.15</v>
       </c>
       <c r="I4" t="n">
         <v>3493.251808452384</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.79</v>
+        <v>-5.96</v>
       </c>
       <c r="L4" t="n">
-        <v>4.67</v>
+        <v>6.51</v>
       </c>
       <c r="M4" t="n">
         <v>1.26</v>
       </c>
       <c r="N4" t="n">
-        <v>1.47</v>
+        <v>3.27</v>
       </c>
       <c r="O4" t="n">
         <v>2.97</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>7.51</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42121</v>
+        <v>42122</v>
       </c>
       <c r="H5" t="n">
-        <v>3648.4</v>
+        <v>3822.6</v>
       </c>
       <c r="I5" t="n">
         <v>3676.055520974391</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.53</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>5.55</v>
+        <v>9.99</v>
       </c>
       <c r="M5" t="n">
         <v>0.78</v>
       </c>
       <c r="N5" t="n">
-        <v>3.02</v>
+        <v>4.77</v>
       </c>
       <c r="O5" t="n">
         <v>-3.27</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>9.74</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H6" t="n">
-        <v>4567.35</v>
+        <v>4241.8</v>
       </c>
       <c r="I6" t="n">
         <v>4418.722399120941</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K6" t="n">
-        <v>19.48</v>
+        <v>10.97</v>
       </c>
       <c r="L6" t="n">
         <v>7.92</v>
       </c>
       <c r="M6" t="n">
-        <v>1.23</v>
+        <v>4.76</v>
       </c>
       <c r="N6" t="n">
-        <v>4.18</v>
+        <v>7.13</v>
       </c>
       <c r="O6" t="n">
         <v>4.77</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>9.73</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42265</v>
+        <v>42268</v>
       </c>
       <c r="H7" t="n">
-        <v>4400.85</v>
+        <v>4490.25</v>
       </c>
       <c r="I7" t="n">
         <v>4409.838848502273</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.75</v>
+        <v>-5.86</v>
       </c>
       <c r="L7" t="n">
-        <v>5.58</v>
+        <v>6.3</v>
       </c>
       <c r="M7" t="n">
         <v>1.71</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>7.86</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42282</v>
+        <v>42283</v>
       </c>
       <c r="H8" t="n">
-        <v>4414.05</v>
+        <v>4354</v>
       </c>
       <c r="I8" t="n">
         <v>4354.33452701171</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.7</v>
+        <v>-3.03</v>
       </c>
       <c r="L8" t="n">
-        <v>2.3</v>
+        <v>3.39</v>
       </c>
       <c r="M8" t="n">
         <v>0.58</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>9.67</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42314</v>
+        <v>42317</v>
       </c>
       <c r="H9" t="n">
-        <v>4522.8</v>
+        <v>4628.2</v>
       </c>
       <c r="I9" t="n">
         <v>4589.88419477761</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.88</v>
+        <v>-6.3</v>
       </c>
       <c r="L9" t="n">
-        <v>4.71</v>
+        <v>6.55</v>
       </c>
       <c r="M9" t="n">
         <v>0.83</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42375</v>
+        <v>42376</v>
       </c>
       <c r="H10" t="n">
-        <v>4480.8</v>
+        <v>4267.9</v>
       </c>
       <c r="I10" t="n">
         <v>4463.417219704043</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.18</v>
+        <v>-7.78</v>
       </c>
       <c r="L10" t="n">
-        <v>4.8</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="M10" t="n">
         <v>1.83</v>
       </c>
       <c r="N10" t="n">
-        <v>2.67</v>
+        <v>4.75</v>
       </c>
       <c r="O10" t="n">
         <v>2.33</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.24</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42450</v>
+        <v>42451</v>
       </c>
       <c r="H11" t="n">
-        <v>3669.55</v>
+        <v>3699.55</v>
       </c>
       <c r="I11" t="n">
         <v>3677.412868751594</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K11" t="n">
-        <v>14.02</v>
+        <v>13.32</v>
       </c>
       <c r="L11" t="n">
         <v>4.26</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>8.18</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42682</v>
+        <v>42683</v>
       </c>
       <c r="H12" t="n">
-        <v>5669</v>
+        <v>5392.95</v>
       </c>
       <c r="I12" t="n">
         <v>5624.523926618749</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K12" t="n">
-        <v>53.23</v>
+        <v>45.77</v>
       </c>
       <c r="L12" t="n">
         <v>7.6</v>
       </c>
       <c r="M12" t="n">
-        <v>2.77</v>
+        <v>6.42</v>
       </c>
       <c r="N12" t="n">
-        <v>3.49</v>
+        <v>4.87</v>
       </c>
       <c r="O12" t="n">
         <v>0.82</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>154</v>
+        <v>155</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>9</v>
+      </c>
+      <c r="U12" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>7.82</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42732</v>
+        <v>42733</v>
       </c>
       <c r="H13" t="n">
-        <v>5231.25</v>
+        <v>5314.8</v>
       </c>
       <c r="I13" t="n">
         <v>5279.994451811474</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>1.45</v>
       </c>
       <c r="L13" t="n">
         <v>2.97</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>6.98</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42780</v>
+        <v>42781</v>
       </c>
       <c r="H14" t="n">
-        <v>5939.85</v>
+        <v>5862.7</v>
       </c>
       <c r="I14" t="n">
         <v>5918.181314043752</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K14" t="n">
-        <v>11.76</v>
+        <v>10.31</v>
       </c>
       <c r="L14" t="n">
         <v>1.84</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>5.82</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42809</v>
+        <v>42810</v>
       </c>
       <c r="H15" t="n">
-        <v>6137.35</v>
+        <v>6155.45</v>
       </c>
       <c r="I15" t="n">
         <v>6140.528078725932</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.68</v>
+        <v>-4.99</v>
       </c>
       <c r="L15" t="n">
-        <v>5.22</v>
+        <v>5.52</v>
       </c>
       <c r="M15" t="n">
         <v>1.75</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>4.66</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42957</v>
+        <v>42958</v>
       </c>
       <c r="H16" t="n">
-        <v>7578.75</v>
+        <v>7457.4</v>
       </c>
       <c r="I16" t="n">
         <v>7488.656078884789</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K16" t="n">
-        <v>23.12</v>
+        <v>21.15</v>
       </c>
       <c r="L16" t="n">
         <v>3.67</v>
       </c>
       <c r="M16" t="n">
-        <v>0.66</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
         <v>1.83</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>5.2</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42983</v>
+        <v>42984</v>
       </c>
       <c r="H17" t="n">
-        <v>7817.2</v>
+        <v>7846.65</v>
       </c>
       <c r="I17" t="n">
         <v>7844.98188414369</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.82</v>
+        <v>-5.22</v>
       </c>
       <c r="L17" t="n">
-        <v>5.61</v>
+        <v>5.99</v>
       </c>
       <c r="M17" t="n">
         <v>1.08</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>4.76</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H18" t="n">
-        <v>7889.9</v>
+        <v>7739.95</v>
       </c>
       <c r="I18" t="n">
         <v>7836.860525455588</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K18" t="n">
-        <v>0.55</v>
+        <v>-1.36</v>
       </c>
       <c r="L18" t="n">
-        <v>0.98</v>
+        <v>1.68</v>
       </c>
       <c r="M18" t="n">
         <v>0.24</v>
       </c>
       <c r="N18" t="n">
-        <v>1.28</v>
+        <v>1.9</v>
       </c>
       <c r="O18" t="n">
         <v>0.38</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>6.42</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43035</v>
+        <v>43038</v>
       </c>
       <c r="H19" t="n">
-        <v>8114.45</v>
+        <v>8195.25</v>
       </c>
       <c r="I19" t="n">
         <v>8130.110580056552</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.84</v>
+        <v>-5.88</v>
       </c>
       <c r="L19" t="n">
-        <v>6.46</v>
+        <v>6.96</v>
       </c>
       <c r="M19" t="n">
-        <v>0.97</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
         <v>2.51</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.63</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H20" t="n">
-        <v>9401.85</v>
+        <v>8990.6</v>
       </c>
       <c r="I20" t="n">
         <v>9223.825709122537</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K20" t="n">
-        <v>14.72</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="L20" t="n">
         <v>1.41</v>
@@ -1581,7 +1820,7 @@
         <v>0.61</v>
       </c>
       <c r="N20" t="n">
-        <v>1.66</v>
+        <v>4.37</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43194</v>
+        <v>43195</v>
       </c>
       <c r="H21" t="n">
-        <v>9013.5</v>
+        <v>9132.6</v>
       </c>
       <c r="I21" t="n">
         <v>9079.540449848859</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.25</v>
+        <v>-1.58</v>
       </c>
       <c r="L21" t="n">
         <v>4.1</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>5.85</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43216</v>
+        <v>43217</v>
       </c>
       <c r="H22" t="n">
-        <v>8946.450000000001</v>
+        <v>8783.35</v>
       </c>
       <c r="I22" t="n">
         <v>8813.536418950498</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.04</v>
+        <v>-3.82</v>
       </c>
       <c r="L22" t="n">
-        <v>2.66</v>
+        <v>4.57</v>
       </c>
       <c r="M22" t="n">
         <v>0.26</v>
       </c>
       <c r="N22" t="n">
-        <v>1.43</v>
+        <v>1.82</v>
       </c>
       <c r="O22" t="n">
         <v>1.32</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>7.16</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43256</v>
+        <v>43257</v>
       </c>
       <c r="H23" t="n">
-        <v>8810.4</v>
+        <v>8842.35</v>
       </c>
       <c r="I23" t="n">
         <v>8813.212002019118</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.31</v>
+        <v>-0.67</v>
       </c>
       <c r="L23" t="n">
         <v>4.03</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.13</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43313</v>
+        <v>43314</v>
       </c>
       <c r="H24" t="n">
-        <v>9341.6</v>
+        <v>9142.4</v>
       </c>
       <c r="I24" t="n">
         <v>9283.394183473119</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K24" t="n">
-        <v>5.65</v>
+        <v>3.39</v>
       </c>
       <c r="L24" t="n">
         <v>1.21</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>7.78</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43417</v>
+        <v>43418</v>
       </c>
       <c r="H25" t="n">
-        <v>7150.45</v>
+        <v>7369.05</v>
       </c>
       <c r="I25" t="n">
         <v>7365.152251298156</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K25" t="n">
-        <v>21.79</v>
+        <v>19.4</v>
       </c>
       <c r="L25" t="n">
         <v>3.56</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>10.91</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43439</v>
+        <v>43440</v>
       </c>
       <c r="H26" t="n">
-        <v>7554.05</v>
+        <v>7209.7</v>
       </c>
       <c r="I26" t="n">
         <v>7229.786981781395</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K26" t="n">
-        <v>2.51</v>
+        <v>-2.16</v>
       </c>
       <c r="L26" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="M26" t="n">
-        <v>0.41</v>
+        <v>1.38</v>
       </c>
       <c r="N26" t="n">
-        <v>2.17</v>
+        <v>4.56</v>
       </c>
       <c r="O26" t="n">
         <v>3.06</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43452</v>
+        <v>43453</v>
       </c>
       <c r="H27" t="n">
-        <v>7772.35</v>
+        <v>7936</v>
       </c>
       <c r="I27" t="n">
         <v>7846.324894877904</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.8</v>
+        <v>-10.07</v>
       </c>
       <c r="L27" t="n">
-        <v>8.19</v>
+        <v>10.26</v>
       </c>
       <c r="M27" t="n">
         <v>0.48</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>7.69</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43466</v>
+        <v>43467</v>
       </c>
       <c r="H28" t="n">
-        <v>7476.8</v>
+        <v>7267.85</v>
       </c>
       <c r="I28" t="n">
         <v>7326.029790716192</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
-        <v>-5.79</v>
+        <v>-8.42</v>
       </c>
       <c r="L28" t="n">
-        <v>6.82</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="M28" t="n">
         <v>1.08</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43500</v>
+        <v>43501</v>
       </c>
       <c r="H29" t="n">
-        <v>6988.2</v>
+        <v>7093.6</v>
       </c>
       <c r="I29" t="n">
         <v>7077.340703288398</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K29" t="n">
-        <v>3.85</v>
+        <v>2.4</v>
       </c>
       <c r="L29" t="n">
         <v>3.59</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>9.640000000000001</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43543</v>
+        <v>43544</v>
       </c>
       <c r="H30" t="n">
-        <v>6825.2</v>
+        <v>6673.55</v>
       </c>
       <c r="I30" t="n">
         <v>6702.389300018111</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.78</v>
+        <v>-5.92</v>
       </c>
       <c r="L30" t="n">
-        <v>5.34</v>
+        <v>6.25</v>
       </c>
       <c r="M30" t="n">
         <v>0.77</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>8.380000000000001</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43557</v>
+        <v>43558</v>
       </c>
       <c r="H31" t="n">
-        <v>6889.7</v>
+        <v>7072.9</v>
       </c>
       <c r="I31" t="n">
         <v>7004.292201247966</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.24</v>
+        <v>-5.98</v>
       </c>
       <c r="L31" t="n">
-        <v>3.4</v>
+        <v>6.36</v>
       </c>
       <c r="M31" t="n">
         <v>0.87</v>
       </c>
       <c r="N31" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="O31" t="n">
         <v>-2.22</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>7.91</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43577</v>
+        <v>43578</v>
       </c>
       <c r="H32" t="n">
-        <v>7321.25</v>
+        <v>7048.9</v>
       </c>
       <c r="I32" t="n">
         <v>7095.388475523405</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K32" t="n">
-        <v>3.51</v>
+        <v>-0.34</v>
       </c>
       <c r="L32" t="n">
         <v>2.5</v>
@@ -2265,7 +2648,7 @@
         <v>0.34</v>
       </c>
       <c r="N32" t="n">
-        <v>1.69</v>
+        <v>3.72</v>
       </c>
       <c r="O32" t="n">
         <v>2.66</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H33" t="n">
-        <v>6706.85</v>
+        <v>7084.6</v>
       </c>
       <c r="I33" t="n">
         <v>6900.702532647185</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K33" t="n">
-        <v>4.85</v>
+        <v>-0.51</v>
       </c>
       <c r="L33" t="n">
         <v>4.82</v>
       </c>
       <c r="M33" t="n">
-        <v>0.53</v>
+        <v>2.51</v>
       </c>
       <c r="N33" t="n">
-        <v>3.51</v>
+        <v>5.63</v>
       </c>
       <c r="O33" t="n">
         <v>-3.72</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>8.94</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43633</v>
+        <v>43634</v>
       </c>
       <c r="H34" t="n">
-        <v>6581.65</v>
+        <v>6439</v>
       </c>
       <c r="I34" t="n">
         <v>6498.584330525433</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K34" t="n">
-        <v>-7.1</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M34" t="n">
         <v>1.6</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43685</v>
+        <v>43686</v>
       </c>
       <c r="H35" t="n">
-        <v>5902.25</v>
+        <v>6099.9</v>
       </c>
       <c r="I35" t="n">
         <v>6033.674143916255</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K35" t="n">
-        <v>8.34</v>
+        <v>5.27</v>
       </c>
       <c r="L35" t="n">
         <v>3.26</v>
@@ -2436,7 +2855,7 @@
         <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>2.99</v>
+        <v>3.35</v>
       </c>
       <c r="O35" t="n">
         <v>-2.17</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.44</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43804</v>
+        <v>43805</v>
       </c>
       <c r="H36" t="n">
-        <v>7012.85</v>
+        <v>6886.7</v>
       </c>
       <c r="I36" t="n">
         <v>6989.047055989753</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K36" t="n">
-        <v>14.97</v>
+        <v>12.9</v>
       </c>
       <c r="L36" t="n">
         <v>8.359999999999999</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43844</v>
+        <v>43845</v>
       </c>
       <c r="H37" t="n">
-        <v>7386.8</v>
+        <v>7482.95</v>
       </c>
       <c r="I37" t="n">
         <v>7435.976025727648</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K37" t="n">
-        <v>-7.26</v>
+        <v>-8.66</v>
       </c>
       <c r="L37" t="n">
-        <v>7.92</v>
+        <v>8.98</v>
       </c>
       <c r="M37" t="n">
         <v>1.75</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>5.89</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43857</v>
+        <v>43858</v>
       </c>
       <c r="H38" t="n">
-        <v>7148.8</v>
+        <v>6997.05</v>
       </c>
       <c r="I38" t="n">
         <v>7119.832437875146</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.47</v>
+        <v>-6.49</v>
       </c>
       <c r="L38" t="n">
-        <v>5.64</v>
+        <v>6.95</v>
       </c>
       <c r="M38" t="n">
         <v>0.51</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>7.74</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43937</v>
+        <v>43938</v>
       </c>
       <c r="H39" t="n">
-        <v>5130.8</v>
+        <v>5505</v>
       </c>
       <c r="I39" t="n">
         <v>5391.525856678628</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K39" t="n">
-        <v>26.67</v>
+        <v>21.32</v>
       </c>
       <c r="L39" t="n">
         <v>3.35</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>25.18</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44092</v>
+        <v>44095</v>
       </c>
       <c r="H40" t="n">
-        <v>6964.75</v>
+        <v>6626.95</v>
       </c>
       <c r="I40" t="n">
         <v>6728.752511552158</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="K40" t="n">
-        <v>26.52</v>
+        <v>20.38</v>
       </c>
       <c r="L40" t="n">
         <v>15.76</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>11.37</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44110</v>
+        <v>44111</v>
       </c>
       <c r="H41" t="n">
-        <v>6892.4</v>
+        <v>7046.9</v>
       </c>
       <c r="I41" t="n">
         <v>7016.066628752335</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.01</v>
+        <v>-6.34</v>
       </c>
       <c r="L41" t="n">
-        <v>5.43</v>
+        <v>6.69</v>
       </c>
       <c r="M41" t="n">
         <v>1.55</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>8.94</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44223</v>
+        <v>44224</v>
       </c>
       <c r="H42" t="n">
-        <v>7870.9</v>
+        <v>7588.5</v>
       </c>
       <c r="I42" t="n">
         <v>7604.310570440253</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K42" t="n">
-        <v>11.69</v>
+        <v>7.69</v>
       </c>
       <c r="L42" t="n">
         <v>4.17</v>
@@ -2835,7 +3338,7 @@
         <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>2.61</v>
+        <v>3.59</v>
       </c>
       <c r="O42" t="n">
         <v>2.24</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>12.27</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44341</v>
+        <v>44342</v>
       </c>
       <c r="H43" t="n">
-        <v>6911.8</v>
+        <v>7034.3</v>
       </c>
       <c r="I43" t="n">
         <v>6990.660817614182</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K43" t="n">
-        <v>8.92</v>
+        <v>7.3</v>
       </c>
       <c r="L43" t="n">
         <v>5.22</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>6.33</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44363</v>
+        <v>44364</v>
       </c>
       <c r="H44" t="n">
-        <v>7114.25</v>
+        <v>6969.35</v>
       </c>
       <c r="I44" t="n">
         <v>6974.140228072751</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K44" t="n">
-        <v>1.14</v>
+        <v>-0.92</v>
       </c>
       <c r="L44" t="n">
         <v>1.74</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4</v>
+        <v>0.76</v>
       </c>
       <c r="N44" t="n">
-        <v>1.33</v>
+        <v>2.04</v>
       </c>
       <c r="O44" t="n">
         <v>1.77</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>5.78</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44368</v>
+        <v>44369</v>
       </c>
       <c r="H45" t="n">
-        <v>6899.9</v>
+        <v>7265.4</v>
       </c>
       <c r="I45" t="n">
         <v>7253.422115656508</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>-4.25</v>
       </c>
       <c r="L45" t="n">
-        <v>1.86</v>
+        <v>4.74</v>
       </c>
       <c r="M45" t="n">
-        <v>0.29</v>
+        <v>0.58</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O45" t="n">
         <v>-2.04</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44393</v>
+        <v>44396</v>
       </c>
       <c r="H46" t="n">
-        <v>7303.55</v>
+        <v>7165.55</v>
       </c>
       <c r="I46" t="n">
         <v>7216.407044360212</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K46" t="n">
-        <v>0.53</v>
+        <v>-1.37</v>
       </c>
       <c r="L46" t="n">
         <v>4.62</v>
       </c>
       <c r="M46" t="n">
-        <v>0.27</v>
+        <v>0.71</v>
       </c>
       <c r="N46" t="n">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="O46" t="n">
         <v>5.3</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>6.21</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44463</v>
+        <v>44466</v>
       </c>
       <c r="H47" t="n">
-        <v>6952.25</v>
+        <v>7403.45</v>
       </c>
       <c r="I47" t="n">
         <v>7044.792939147247</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K47" t="n">
-        <v>2.98</v>
+        <v>-3.32</v>
       </c>
       <c r="L47" t="n">
-        <v>2.92</v>
+        <v>3.94</v>
       </c>
       <c r="M47" t="n">
         <v>1.75</v>
       </c>
       <c r="N47" t="n">
-        <v>2.6</v>
+        <v>6.49</v>
       </c>
       <c r="O47" t="n">
         <v>-1.89</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.99</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H48" t="n">
-        <v>7572.5</v>
+        <v>7170.5</v>
       </c>
       <c r="I48" t="n">
         <v>7489.53166754875</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K48" t="n">
-        <v>2.28</v>
+        <v>-3.15</v>
       </c>
       <c r="L48" t="n">
         <v>5.8</v>
@@ -3177,7 +3752,7 @@
         <v>1.61</v>
       </c>
       <c r="N48" t="n">
-        <v>3.11</v>
+        <v>5.31</v>
       </c>
       <c r="O48" t="n">
         <v>6.49</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>13.51</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44566</v>
+        <v>44567</v>
       </c>
       <c r="H49" t="n">
-        <v>7775.35</v>
+        <v>7882.1</v>
       </c>
       <c r="I49" t="n">
         <v>7827.918084001222</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K49" t="n">
-        <v>-8.44</v>
+        <v>-9.92</v>
       </c>
       <c r="L49" t="n">
-        <v>8.890000000000001</v>
+        <v>10.17</v>
       </c>
       <c r="M49" t="n">
         <v>1.74</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.87</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44620</v>
+        <v>44622</v>
       </c>
       <c r="H50" t="n">
-        <v>8314.15</v>
+        <v>7814.2</v>
       </c>
       <c r="I50" t="n">
         <v>8011.654207294124</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K50" t="n">
-        <v>5.48</v>
+        <v>-0.86</v>
       </c>
       <c r="L50" t="n">
         <v>2.51</v>
@@ -3291,7 +3890,7 @@
         <v>3.41</v>
       </c>
       <c r="N50" t="n">
-        <v>5.62</v>
+        <v>6.01</v>
       </c>
       <c r="O50" t="n">
         <v>1.37</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>13.83</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44641</v>
+        <v>44642</v>
       </c>
       <c r="H51" t="n">
-        <v>7705.55</v>
+        <v>7766.65</v>
       </c>
       <c r="I51" t="n">
         <v>7727.042345526603</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K51" t="n">
-        <v>1.39</v>
+        <v>0.61</v>
       </c>
       <c r="L51" t="n">
         <v>4.92</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>12.67</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44692</v>
+        <v>44693</v>
       </c>
       <c r="H52" t="n">
-        <v>7396.45</v>
+        <v>7253.65</v>
       </c>
       <c r="I52" t="n">
         <v>7264.659205442227</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.77</v>
+        <v>-6.61</v>
       </c>
       <c r="L52" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>1.27</v>
+        <v>2.37</v>
       </c>
       <c r="N52" t="n">
         <v>3.1</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44707</v>
+        <v>44708</v>
       </c>
       <c r="H53" t="n">
-        <v>7805</v>
+        <v>7942.95</v>
       </c>
       <c r="I53" t="n">
         <v>7911.877335701062</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K53" t="n">
-        <v>-7.6</v>
+        <v>-9.5</v>
       </c>
       <c r="L53" t="n">
-        <v>9.67</v>
+        <v>9.82</v>
       </c>
       <c r="M53" t="n">
         <v>2.81</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.84</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44831</v>
+        <v>44832</v>
       </c>
       <c r="H54" t="n">
-        <v>8774.049999999999</v>
+        <v>8726.75</v>
       </c>
       <c r="I54" t="n">
         <v>8743.229965698769</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K54" t="n">
-        <v>10.46</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="L54" t="n">
         <v>4.88</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>8.42</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44861</v>
+        <v>44862</v>
       </c>
       <c r="H55" t="n">
-        <v>9041.950000000001</v>
+        <v>9492.549999999999</v>
       </c>
       <c r="I55" t="n">
         <v>9251.940344452049</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K55" t="n">
-        <v>-3.61</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>4.01</v>
+        <v>9.43</v>
       </c>
       <c r="M55" t="n">
         <v>1.78</v>
       </c>
       <c r="N55" t="n">
-        <v>2.73</v>
+        <v>4.98</v>
       </c>
       <c r="O55" t="n">
         <v>-0.54</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44882</v>
+        <v>44883</v>
       </c>
       <c r="H56" t="n">
-        <v>8986.450000000001</v>
+        <v>8848.049999999999</v>
       </c>
       <c r="I56" t="n">
         <v>8929.504099504058</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K56" t="n">
-        <v>-5.33</v>
+        <v>-6.79</v>
       </c>
       <c r="L56" t="n">
-        <v>5.5</v>
+        <v>6.92</v>
       </c>
       <c r="M56" t="n">
         <v>0.57</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>7.28</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44949</v>
+        <v>44950</v>
       </c>
       <c r="H57" t="n">
-        <v>8417.1</v>
+        <v>8698.799999999999</v>
       </c>
       <c r="I57" t="n">
         <v>8689.202755655571</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K57" t="n">
-        <v>4.87</v>
+        <v>1.69</v>
       </c>
       <c r="L57" t="n">
         <v>2.89</v>
@@ -3690,7 +4373,7 @@
         <v>0.75</v>
       </c>
       <c r="N57" t="n">
-        <v>1.41</v>
+        <v>3.35</v>
       </c>
       <c r="O57" t="n">
         <v>-1.54</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>6.31</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45001</v>
+        <v>45002</v>
       </c>
       <c r="H58" t="n">
-        <v>8437.450000000001</v>
+        <v>8316.85</v>
       </c>
       <c r="I58" t="n">
         <v>8436.744216690187</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K58" t="n">
-        <v>-3</v>
+        <v>-4.39</v>
       </c>
       <c r="L58" t="n">
-        <v>3.31</v>
+        <v>4.66</v>
       </c>
       <c r="M58" t="n">
         <v>0.37</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>6.56</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45029</v>
+        <v>45033</v>
       </c>
       <c r="H59" t="n">
-        <v>8670.799999999999</v>
+        <v>8674.65</v>
       </c>
       <c r="I59" t="n">
         <v>8672.28102802646</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.26</v>
+        <v>-4.3</v>
       </c>
       <c r="L59" t="n">
-        <v>4.73</v>
+        <v>6.41</v>
       </c>
       <c r="M59" t="n">
-        <v>1.46</v>
+        <v>2.07</v>
       </c>
       <c r="N59" t="n">
         <v>2.54</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>4.22</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45148</v>
+        <v>45149</v>
       </c>
       <c r="H60" t="n">
-        <v>9397.6</v>
+        <v>9356.85</v>
       </c>
       <c r="I60" t="n">
         <v>9392.324025667085</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K60" t="n">
-        <v>8.33</v>
+        <v>7.86</v>
       </c>
       <c r="L60" t="n">
         <v>2.94</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>5.7</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45167</v>
+        <v>45168</v>
       </c>
       <c r="H61" t="n">
-        <v>9621.25</v>
+        <v>9796.4</v>
       </c>
       <c r="I61" t="n">
         <v>9777.729823559319</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.83</v>
+        <v>-4.7</v>
       </c>
       <c r="L61" t="n">
-        <v>3.5</v>
+        <v>4.93</v>
       </c>
       <c r="M61" t="n">
         <v>0.63</v>
       </c>
       <c r="N61" t="n">
-        <v>1.15</v>
+        <v>1.82</v>
       </c>
       <c r="O61" t="n">
         <v>-0.43</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>5.51</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45230</v>
+        <v>45231</v>
       </c>
       <c r="H62" t="n">
-        <v>10392.3</v>
+        <v>10227.75</v>
       </c>
       <c r="I62" t="n">
         <v>10262.64991074091</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K62" t="n">
-        <v>6.08</v>
+        <v>4.4</v>
       </c>
       <c r="L62" t="n">
         <v>1.9</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>7.08</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="H63" t="n">
-        <v>10186.9</v>
+        <v>10637.95</v>
       </c>
       <c r="I63" t="n">
         <v>10392.113782442</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K63" t="n">
-        <v>0.4</v>
+        <v>-4.01</v>
       </c>
       <c r="L63" t="n">
         <v>6.89</v>
@@ -4032,7 +4787,7 @@
         <v>1.55</v>
       </c>
       <c r="N63" t="n">
-        <v>2.36</v>
+        <v>4.43</v>
       </c>
       <c r="O63" t="n">
         <v>-1.58</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4</v>
+      </c>
+      <c r="U63" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>7.77</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45470</v>
+        <v>45471</v>
       </c>
       <c r="H64" t="n">
-        <v>12178.75</v>
+        <v>12033.85</v>
       </c>
       <c r="I64" t="n">
         <v>12089.41863701885</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K64" t="n">
-        <v>14.48</v>
+        <v>13.12</v>
       </c>
       <c r="L64" t="n">
         <v>4.08</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>6</v>
+      </c>
+      <c r="U64" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>7.03</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45481</v>
+        <v>45482</v>
       </c>
       <c r="H65" t="n">
-        <v>12023.6</v>
+        <v>12827.7</v>
       </c>
       <c r="I65" t="n">
         <v>12677.84658209869</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K65" t="n">
-        <v>0.09</v>
+        <v>-6.6</v>
       </c>
       <c r="L65" t="n">
-        <v>1.88</v>
+        <v>7.7</v>
       </c>
       <c r="M65" t="n">
-        <v>0.6</v>
+        <v>2.51</v>
       </c>
       <c r="N65" t="n">
-        <v>0.67</v>
+        <v>6.69</v>
       </c>
       <c r="O65" t="n">
         <v>-1.19</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,25 +4973,25 @@
         <v>8.35</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H66" t="n">
-        <v>12726.4</v>
+        <v>12200.85</v>
       </c>
       <c r="I66" t="n">
         <v>12463.16793398566</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.79</v>
+        <v>-4.89</v>
       </c>
       <c r="L66" t="n">
-        <v>4.39</v>
+        <v>6.24</v>
       </c>
       <c r="M66" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="N66" t="n">
         <v>4.74</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>9.9</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45558</v>
+        <v>45559</v>
       </c>
       <c r="H67" t="n">
-        <v>12683.1</v>
+        <v>12738.6</v>
       </c>
       <c r="I67" t="n">
         <v>12735.9989270541</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.95</v>
+        <v>-4.41</v>
       </c>
       <c r="L67" t="n">
-        <v>4.49</v>
+        <v>4.74</v>
       </c>
       <c r="M67" t="n">
         <v>2.21</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>4.94</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H68" t="n">
-        <v>13166</v>
+        <v>12647.35</v>
       </c>
       <c r="I68" t="n">
         <v>12692.11127900673</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K68" t="n">
-        <v>3.36</v>
+        <v>-0.72</v>
       </c>
       <c r="L68" t="n">
         <v>1.22</v>
       </c>
       <c r="M68" t="n">
-        <v>1.13</v>
+        <v>1.71</v>
       </c>
       <c r="N68" t="n">
-        <v>1.91</v>
+        <v>3.94</v>
       </c>
       <c r="O68" t="n">
         <v>0.44</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="H69" t="n">
-        <v>11208.3</v>
+        <v>11841.3</v>
       </c>
       <c r="I69" t="n">
         <v>11403.03007247765</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K69" t="n">
-        <v>11.38</v>
+        <v>6.37</v>
       </c>
       <c r="L69" t="n">
         <v>3.96</v>
@@ -4374,7 +5201,7 @@
         <v>1.67</v>
       </c>
       <c r="N69" t="n">
-        <v>3.22</v>
+        <v>5.65</v>
       </c>
       <c r="O69" t="n">
         <v>-3.94</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>4</v>
+      </c>
+      <c r="U69" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>9.34</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45715</v>
+        <v>45716</v>
       </c>
       <c r="H70" t="n">
-        <v>12380.6</v>
+        <v>11945.85</v>
       </c>
       <c r="I70" t="n">
         <v>12217.32344027491</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K70" t="n">
-        <v>4.55</v>
+        <v>0.88</v>
       </c>
       <c r="L70" t="n">
         <v>5.2</v>
@@ -4431,7 +5270,7 @@
         <v>1.4</v>
       </c>
       <c r="N70" t="n">
-        <v>1.94</v>
+        <v>3.51</v>
       </c>
       <c r="O70" t="n">
         <v>5.65</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>7.49</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45776</v>
+        <v>45777</v>
       </c>
       <c r="H71" t="n">
-        <v>11841</v>
+        <v>12257</v>
       </c>
       <c r="I71" t="n">
         <v>12021.76443384298</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K71" t="n">
-        <v>0.88</v>
+        <v>-2.6</v>
       </c>
       <c r="L71" t="n">
         <v>3.29</v>
@@ -4488,7 +5339,7 @@
         <v>1.77</v>
       </c>
       <c r="N71" t="n">
-        <v>2.21</v>
+        <v>3.51</v>
       </c>
       <c r="O71" t="n">
         <v>-3.51</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45810</v>
+        <v>45811</v>
       </c>
       <c r="H72" t="n">
-        <v>12290</v>
+        <v>12128</v>
       </c>
       <c r="I72" t="n">
         <v>12131.78868653104</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K72" t="n">
-        <v>0.27</v>
+        <v>-1.05</v>
       </c>
       <c r="L72" t="n">
         <v>3.73</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>6.27</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="H73" t="n">
-        <v>12748</v>
+        <v>12806</v>
       </c>
       <c r="I73" t="n">
         <v>12794.32348756324</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K73" t="n">
-        <v>-5.11</v>
+        <v>-5.59</v>
       </c>
       <c r="L73" t="n">
         <v>6.2</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>5.41</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="H74" t="n">
-        <v>16186</v>
+        <v>15651</v>
       </c>
       <c r="I74" t="n">
         <v>15787.26121677436</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K74" t="n">
-        <v>26.39</v>
+        <v>22.22</v>
       </c>
       <c r="L74" t="n">
         <v>4.54</v>
       </c>
       <c r="M74" t="n">
-        <v>0.89</v>
+        <v>1.05</v>
       </c>
       <c r="N74" t="n">
-        <v>2.43</v>
+        <v>3.31</v>
       </c>
       <c r="O74" t="n">
         <v>0.45</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>6</v>
+      </c>
+      <c r="U74" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>6.98</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="H75" t="n">
-        <v>15994</v>
+        <v>16282</v>
       </c>
       <c r="I75" t="n">
         <v>16260.50063699599</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K75" t="n">
-        <v>-2.19</v>
+        <v>-4.03</v>
       </c>
       <c r="L75" t="n">
-        <v>3.9</v>
+        <v>4.39</v>
       </c>
       <c r="M75" t="n">
         <v>1.04</v>
       </c>
       <c r="N75" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="O75" t="n">
         <v>-3.31</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>5.54</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="H76" t="n">
-        <v>16664</v>
+        <v>16501</v>
       </c>
       <c r="I76" t="n">
         <v>16517.42647737668</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K76" t="n">
-        <v>2.35</v>
+        <v>1.35</v>
       </c>
       <c r="L76" t="n">
         <v>2.19</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>5.57</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H77" t="n">
-        <v>12798</v>
+        <v>13602</v>
       </c>
       <c r="I77" t="n">
         <v>13410.18777340086</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K77" t="n">
-        <v>22.44</v>
+        <v>17.57</v>
       </c>
       <c r="L77" t="n">
         <v>1.36</v>
@@ -4830,7 +5753,7 @@
         <v>5.67</v>
       </c>
       <c r="N77" t="n">
-        <v>2.77</v>
+        <v>6.28</v>
       </c>
       <c r="O77" t="n">
         <v>-0.98</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>4</v>
+      </c>
+      <c r="U77" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>10.54</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="H78" t="n">
-        <v>13695</v>
+        <v>13489</v>
       </c>
       <c r="I78" t="n">
         <v>13547.71781817338</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K78" t="n">
-        <v>0.68</v>
+        <v>-0.83</v>
       </c>
       <c r="L78" t="n">
         <v>6.63</v>
@@ -4896,7 +5831,19 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>4</v>
+      </c>
+      <c r="U78" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>7.98</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="H79" t="n">
-        <v>14188</v>
+        <v>14234</v>
       </c>
       <c r="I79" t="n">
         <v>14223.67171964558</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K79" t="n">
-        <v>-5.18</v>
+        <v>-5.52</v>
       </c>
       <c r="L79" t="n">
-        <v>5.64</v>
+        <v>6.37</v>
       </c>
       <c r="M79" t="n">
         <v>1.02</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,28 +5939,28 @@
         <v>6.06</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="H80" t="n">
-        <v>13547</v>
+        <v>12950</v>
       </c>
       <c r="I80" t="n">
         <v>13370.87438626648</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K80" t="n">
-        <v>-4.83</v>
+        <v>-9.02</v>
       </c>
       <c r="L80" t="n">
-        <v>6.79</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M80" t="n">
         <v>1.91</v>
       </c>
       <c r="N80" t="n">
-        <v>1.77</v>
+        <v>4.41</v>
       </c>
       <c r="O80" t="n">
         <v>0.32</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5061,6 +6032,14 @@
       <c r="Q81" t="n">
         <v>39</v>
       </c>
+      <c r="R81" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10019,7 +10998,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.4</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="6">
@@ -10029,7 +11008,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -10039,7 +11018,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8">
@@ -10049,7 +11028,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -10059,7 +11038,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66.5</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="10">
@@ -10069,7 +11048,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>115.4</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11">
@@ -10079,7 +11058,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -10089,7 +11068,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -10099,7 +11078,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>41.8</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="14">
@@ -10109,7 +11088,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.33</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="15">
@@ -10119,7 +11098,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.54</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="16">
@@ -10129,7 +11108,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.06</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="17">
@@ -10139,7 +11118,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>53.23</v>
+        <v>45.77</v>
       </c>
     </row>
     <row r="18">
@@ -10149,7 +11128,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.4</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="19">
@@ -10159,7 +11138,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.6</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="20">
@@ -10169,7 +11148,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.26</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="21">
@@ -10189,7 +11168,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
@@ -10199,7 +11178,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -10209,7 +11188,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="25">
@@ -10219,7 +11198,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.67</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="26">
@@ -10229,7 +11208,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.08</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="27">
@@ -10249,7 +11228,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
